--- a/data/trans_dic/P20D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 100,0</t>
+          <t>11,95; 100,0</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 48,81</t>
+          <t>2,12; 49,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 52,11</t>
+          <t>5,77; 49,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 86,27</t>
+          <t>32,9; 86,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,63; 56,75</t>
+          <t>16,35; 55,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 67,71</t>
+          <t>31,15; 66,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,55; 95,41</t>
+          <t>54,32; 94,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 61,62</t>
+          <t>11,51; 58,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,71; 80,76</t>
+          <t>45,86; 79,59</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,45; 93,66</t>
+          <t>67,24; 93,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,53; 83,31</t>
+          <t>19,66; 83,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,96; 88,44</t>
+          <t>58,62; 86,82</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,03; 91,2</t>
+          <t>25,55; 90,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,55; 64,72</t>
+          <t>21,44; 64,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,14; 68,72</t>
+          <t>32,18; 69,21</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>58,54; 80,67</t>
+          <t>58,73; 80,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,26; 53,16</t>
+          <t>25,77; 51,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,82; 64,54</t>
+          <t>47,09; 65,0</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>736; 3220</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>736; 3220</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>972; 7710</t>
+          <t>922; 7710</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48; 4987</t>
+          <t>0; 4987</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158; 3970</t>
+          <t>172; 3994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1028; 6836</t>
+          <t>758; 6523</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4718; 12285</t>
+          <t>4685; 12249</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2097; 7158</t>
+          <t>2063; 6943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8482; 18183</t>
+          <t>8364; 17724</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9751; 16452</t>
+          <t>9366; 16287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>970; 5215</t>
+          <t>974; 4915</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11752; 20760</t>
+          <t>11789; 20461</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9575; 13702</t>
+          <t>9837; 13750</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>926; 3951</t>
+          <t>932; 3959</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11421; 17132</t>
+          <t>11354; 16818</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1605; 5622</t>
+          <t>1575; 5570</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2150; 6455</t>
+          <t>2138; 6400</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5186; 11091</t>
+          <t>5192; 11169</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36456; 50242</t>
+          <t>36577; 50411</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14084; 26495</t>
+          <t>12843; 25658</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53611; 72362</t>
+          <t>52796; 72878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Edad-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 100,0</t>
+          <t>12,11; 100,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 84,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 49,11</t>
+          <t>6,14; 47,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 49,72</t>
+          <t>12,76; 61,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,9; 86,02</t>
+          <t>39,82; 87,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 55,05</t>
+          <t>19,21; 59,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,15; 66,0</t>
+          <t>35,9; 71,29</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,32; 94,46</t>
+          <t>55,88; 92,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 58,07</t>
+          <t>16,25; 62,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,86; 79,59</t>
+          <t>44,99; 76,93</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,24; 93,99</t>
+          <t>65,25; 94,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,66; 83,49</t>
+          <t>18,62; 81,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,62; 86,82</t>
+          <t>59,28; 86,54</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,55; 90,36</t>
+          <t>22,88; 91,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,44; 64,16</t>
+          <t>21,72; 66,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,18; 69,21</t>
+          <t>32,31; 68,35</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>58,73; 80,95</t>
+          <t>61,02; 82,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,77; 51,48</t>
+          <t>29,01; 52,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,09; 65,0</t>
+          <t>49,15; 64,92</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>947</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4665</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5013</t>
+          <t>0; 4919</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2698</t>
+          <t>0; 2838</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>922; 7710</t>
+          <t>939; 7757</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4370</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4987</t>
+          <t>0; 5033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172; 3994</t>
+          <t>540; 4180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>758; 6523</t>
+          <t>1882; 9092</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>17276</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4685; 12249</t>
+          <t>7041; 15520</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2063; 6943</t>
+          <t>2775; 8629</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8364; 17724</t>
+          <t>11534; 22904</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>17907</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9366; 16287</t>
+          <t>9969; 16565</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>974; 4915</t>
+          <t>1755; 6800</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11789; 20461</t>
+          <t>12884; 22030</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15551</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9837; 13750</t>
+          <t>9928; 14306</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>932; 3959</t>
+          <t>1023; 4462</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11354; 16818</t>
+          <t>12277; 17921</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8919</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1575; 5570</t>
+          <t>1511; 6033</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2138; 6400</t>
+          <t>2453; 7512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5192; 11169</t>
+          <t>5783; 12235</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>72300</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36577; 50411</t>
+          <t>41618; 56405</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12843; 25658</t>
+          <t>16616; 30142</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52796; 72878</t>
+          <t>61674; 81467</t>
         </is>
       </c>
     </row>
